--- a/web/public/templates/employees_template.xlsx
+++ b/web/public/templates/employees_template.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/web/public/templates/employees_template.xlsx
+++ b/web/public/templates/employees_template.xlsx
@@ -623,12 +623,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Required</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Required for employee/vendor roles. Must exist, e.g. VND-001.</t>
+          <t>Vendor the account belongs to. Must exist, e.g. VND-001. RJCorp accounts belong to no vendor and cannot be created from this template — use Onboarding &gt; Employee for those.</t>
         </is>
       </c>
     </row>

--- a/web/public/templates/employees_template.xlsx
+++ b/web/public/templates/employees_template.xlsx
@@ -459,39 +459,39 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>FIRST_NAME</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>LAST_NAME</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>EMAIL</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>ROLE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>MOBILE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>VENDOR_UID</t>
         </is>
       </c>
     </row>
     <row r="2"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user" promptTitle="role" prompt="Choose: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user" type="list">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user" promptTitle="ROLE" prompt="Choose: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user" type="list">
       <formula1>"employee,vendor_admin,vendor_user,rjcorp_admin,rjcorp_user"</formula1>
     </dataValidation>
   </dataValidations>
@@ -533,7 +533,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>FIRST_NAME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>LAST_NAME</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>EMAIL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -584,7 +584,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>ROLE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>mobile</t>
+          <t>MOBILE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>vendor_uid</t>
+          <t>VENDOR_UID</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">

--- a/web/public/templates/employees_template.xlsx
+++ b/web/public/templates/employees_template.xlsx
@@ -73,10 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -491,7 +494,7 @@
     <row r="2"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid value" error="Pick one of: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user" promptTitle="ROLE" prompt="Choose: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user" type="list">
+    <dataValidation sqref="D2:D1000" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="ROLE" prompt="Choose: employee, vendor_admin, vendor_user, rjcorp_admin, rjcorp_user (case does not matter)" type="list">
       <formula1>"employee,vendor_admin,vendor_user,rjcorp_admin,rjcorp_user"</formula1>
     </dataValidation>
   </dataValidations>
@@ -505,134 +508,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="60" customHeight="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Column</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Notes</t>
+          <t>Column names are matched on SPELLING ONLY. Upper or lower case makes no difference, and spaces, hyphens and underscores are treated the same - so CUST_CD, Cust_CD and "cust cd" are the same column. The headers on the Data sheet are all-caps; keep the wording, and the case is up to you. A sheet filled in with Caps Lock on uploads exactly like any other. Do not rename, reorder or delete columns - only the wording identifies them.</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Required</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
           <t>FIRST_NAME</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Given name.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>LAST_NAME</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Family name.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>EMAIL</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Login email (unique).</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>ROLE</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>employee | vendor_admin | vendor_user | rjcorp_admin | rjcorp_user.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>employee | vendor_admin | vendor_user | rjcorp_admin | rjcorp_user. Matched on spelling only, so EMPLOYEE and Employee are equally valid.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>MOBILE</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Mobile number.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>VENDOR_UID</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Required</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Vendor the account belongs to. Must exist, e.g. VND-001. RJCorp accounts belong to no vendor and cannot be created from this template — use Onboarding &gt; Employee for those.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>